--- a/data/cci/cci-platformprog.xlsx
+++ b/data/cci/cci-platformprog.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amw23\Documents\GitHub\cci-vocabularies\data\cci\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stfc365-my.sharepoint.com/personal/alison_waterfall_stfc_ac_uk/Documents/Documents/GitHub/cci-vocabularies/data/cci/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B1F6C34-73B9-47AC-82F4-A5ABC79CC5CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{1B1F6C34-73B9-47AC-82F4-A5ABC79CC5CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31538A35-0CD8-4627-9936-86F531BA60FD}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{4D380965-4325-DA46-9678-A8F4BC4ABC47}"/>
+    <workbookView xWindow="3465" yWindow="3465" windowWidth="34515" windowHeight="15285" xr2:uid="{4D380965-4325-DA46-9678-A8F4BC4ABC47}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="244">
   <si>
     <t>URI</t>
   </si>
@@ -187,6 +187,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Liberation Sans"/>
+        <family val="2"/>
       </rPr>
       <t>st</t>
     </r>
@@ -218,6 +219,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Liberation Sans"/>
+        <family val="2"/>
       </rPr>
       <t>nd</t>
     </r>
@@ -240,6 +242,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Liberation Sans"/>
+        <family val="2"/>
       </rPr>
       <t>nd</t>
     </r>
@@ -268,6 +271,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Liberation Sans"/>
+        <family val="2"/>
       </rPr>
       <t>rd</t>
     </r>
@@ -413,6 +417,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Liberation Sans"/>
+        <family val="2"/>
       </rPr>
       <t>rd</t>
     </r>
@@ -441,6 +446,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Liberation Sans"/>
+        <family val="2"/>
       </rPr>
       <t>th</t>
     </r>
@@ -455,6 +461,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Liberation Sans"/>
+        <family val="2"/>
       </rPr>
       <t>th</t>
     </r>
@@ -483,6 +490,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Liberation Sans"/>
+        <family val="2"/>
       </rPr>
       <t>th</t>
     </r>
@@ -497,6 +505,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Liberation Sans"/>
+        <family val="2"/>
       </rPr>
       <t>th</t>
     </r>
@@ -551,6 +560,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Liberation Sans"/>
+        <family val="2"/>
       </rPr>
       <t>é</t>
     </r>
@@ -567,6 +577,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Liberation Sans"/>
+        <family val="2"/>
       </rPr>
       <t>è</t>
     </r>
@@ -583,6 +594,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Liberation Sans"/>
+        <family val="2"/>
       </rPr>
       <t>é</t>
     </r>
@@ -945,6 +957,18 @@
   </si>
   <si>
     <t>https://space.oscar.wmo.int/satelliteprogrammes/view/iss</t>
+  </si>
+  <si>
+    <t>https://space.oscar.wmo.int/satelliteprogrammes/view/himawari_3rd_generation</t>
+  </si>
+  <si>
+    <t>Himawari 3rd Generation</t>
+  </si>
+  <si>
+    <t>Himawari 3rd Generation programme</t>
+  </si>
+  <si>
+    <t>plat_himawari3rd_prog</t>
   </si>
 </sst>
 </file>
@@ -1044,11 +1068,13 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Liberation Sans"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Liberation Sans"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1177,7 +1203,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1195,7 +1221,6 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="21">
     <cellStyle name="Accent" xfId="7" xr:uid="{0D1E76D5-A312-CD4D-9277-12C830723FF6}"/>
@@ -2578,7 +2603,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1651342F-A944-A646-B5ED-DB0D4005691F}">
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="29.5" style="6" customWidth="1"/>
@@ -3413,7 +3438,7 @@
       <c r="D55" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="E55" s="9" t="s">
+      <c r="E55" t="s">
         <v>226</v>
       </c>
     </row>
@@ -3430,7 +3455,7 @@
       <c r="D56" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="E56" s="9" t="s">
+      <c r="E56" t="s">
         <v>231</v>
       </c>
     </row>
@@ -3444,7 +3469,7 @@
       <c r="D57" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="E57" s="9" t="s">
+      <c r="E57" t="s">
         <v>234</v>
       </c>
     </row>
@@ -3461,8 +3486,22 @@
       <c r="D58" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="E58" s="9" t="s">
+      <c r="E58" t="s">
         <v>239</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>240</v>
       </c>
     </row>
   </sheetData>
